--- a/artfynd/A 29487-2023 artfynd.xlsx
+++ b/artfynd/A 29487-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29487-2023 artfynd.xlsx
+++ b/artfynd/A 29487-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87088018</v>
+        <v>87088467</v>
       </c>
       <c r="B2" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -725,13 +711,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321001.9425076536</v>
+        <v>321044</v>
       </c>
       <c r="R2" t="n">
-        <v>6465044.858473711</v>
+        <v>6465087</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,21 +744,11 @@
           <t>2020-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -785,26 +761,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,15 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87088140</v>
+        <v>87088018</v>
       </c>
       <c r="B3" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321076.9667563362</v>
+        <v>321002</v>
       </c>
       <c r="R3" t="n">
-        <v>6465070.935887053</v>
+        <v>6465045</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,26 +856,11 @@
           <t>2020-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på en granlåga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -937,6 +873,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,40 +910,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87088467</v>
+        <v>87088140</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -995,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321043.9477807083</v>
+        <v>321077</v>
       </c>
       <c r="R4" t="n">
-        <v>6465087.174577305</v>
+        <v>6465071</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,19 +988,14 @@
           <t>2020-07-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-25</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på en granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,15 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87088545</v>
+        <v>87613392</v>
       </c>
       <c r="B5" t="n">
-        <v>90282</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,21 +1038,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4740</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1062,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1122,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321216.2183851498</v>
+        <v>321095</v>
       </c>
       <c r="R5" t="n">
-        <v>6465140.9561712</v>
+        <v>6465107</v>
       </c>
       <c r="S5" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1152,22 +1102,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-07-25</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-07-25</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På stående död gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,11 +1133,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1199,63 +1149,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87613392</v>
+        <v>95486738</v>
       </c>
       <c r="B6" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>1590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Uddevalla, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321094.9517769206</v>
+        <v>321029</v>
       </c>
       <c r="R6" t="n">
-        <v>6465106.971611665</v>
+        <v>6465106</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1279,27 +1216,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På stående död gran.</t>
+          <t>Källpåverkad mark utmed bäckdråg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,15 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95486738</v>
+        <v>87088545</v>
       </c>
       <c r="B7" t="n">
-        <v>95157</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,39 +1264,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1590</v>
+        <v>4740</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Uddevalla, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321028.9440354161</v>
+        <v>321216</v>
       </c>
       <c r="R7" t="n">
-        <v>6465105.228240128</v>
+        <v>6465141</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1398,27 +1328,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Källpåverkad mark utmed bäckdråg.</t>
+          <t>2020-07-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,6 +1344,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1442,6 +1362,126 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6540100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Forshälla, Solfjäll, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>321100</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6465040</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forshälla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2009-02-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2009-02-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>WP181</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
